--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_hoog.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_hoog.xlsx
@@ -400,22 +400,22 @@
         <v>1.414509557120016</v>
       </c>
       <c r="C2">
-        <v>1.320195973509991</v>
+        <v>1.35008299623477</v>
       </c>
       <c r="D2">
         <v>3.992836910096988</v>
       </c>
       <c r="E2">
-        <v>1.346585525682575</v>
+        <v>1.346145053135311</v>
       </c>
       <c r="F2">
         <v>1.414055654904186</v>
       </c>
       <c r="G2">
-        <v>1.378958854892205</v>
+        <v>1.376764628851521</v>
       </c>
       <c r="H2">
-        <v>1.346982622402223</v>
+        <v>1.346536947502336</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -426,22 +426,22 @@
         <v>1.425213289967863</v>
       </c>
       <c r="C3">
-        <v>1.325315907228028</v>
+        <v>1.349339608018896</v>
       </c>
       <c r="D3">
         <v>3.232833313886473</v>
       </c>
       <c r="E3">
-        <v>1.347817107110186</v>
+        <v>1.347368296397462</v>
       </c>
       <c r="F3">
         <v>1.418476688626427</v>
       </c>
       <c r="G3">
-        <v>1.372112685789045</v>
+        <v>1.368056543576119</v>
       </c>
       <c r="H3">
-        <v>1.34782820070677</v>
+        <v>1.347375920831563</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -452,22 +452,22 @@
         <v>1.390138974964715</v>
       </c>
       <c r="C4">
-        <v>1.36634262392983</v>
+        <v>1.351006144102672</v>
       </c>
       <c r="D4">
         <v>3.743511689471815</v>
       </c>
       <c r="E4">
-        <v>1.342443321396813</v>
+        <v>1.341988648295406</v>
       </c>
       <c r="F4">
         <v>1.393836101180277</v>
       </c>
       <c r="G4">
-        <v>1.383240013895821</v>
+        <v>1.365558243147134</v>
       </c>
       <c r="H4">
-        <v>1.342718102337792</v>
+        <v>1.342259846645607</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -478,22 +478,22 @@
         <v>1.423685679465119</v>
       </c>
       <c r="C5">
-        <v>1.409259220543114</v>
+        <v>1.382945653350103</v>
       </c>
       <c r="D5">
         <v>2.286912720564254</v>
       </c>
       <c r="E5">
-        <v>1.350032931609149</v>
+        <v>1.349527612582106</v>
       </c>
       <c r="F5">
         <v>1.414522073045725</v>
       </c>
       <c r="G5">
-        <v>1.399850874782828</v>
+        <v>1.379657500535665</v>
       </c>
       <c r="H5">
-        <v>1.349992015156981</v>
+        <v>1.349487807750695</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -504,22 +504,22 @@
         <v>1.428914950493217</v>
       </c>
       <c r="C6">
-        <v>1.409908246290729</v>
+        <v>1.388846539973</v>
       </c>
       <c r="D6">
         <v>0.5354154108338075</v>
       </c>
       <c r="E6">
-        <v>1.352104465373867</v>
+        <v>1.351597290893297</v>
       </c>
       <c r="F6">
         <v>1.419532925750195</v>
       </c>
       <c r="G6">
-        <v>1.384591965316204</v>
+        <v>1.376020463996002</v>
       </c>
       <c r="H6">
-        <v>1.351843737668599</v>
+        <v>1.351337705383488</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -530,22 +530,22 @@
         <v>1.413520031540222</v>
       </c>
       <c r="C7">
-        <v>1.414435199910633</v>
+        <v>1.394664189341334</v>
       </c>
       <c r="D7">
         <v>0.9101152687398397</v>
       </c>
       <c r="E7">
-        <v>1.3502050541849</v>
+        <v>1.349728347175503</v>
       </c>
       <c r="F7">
         <v>1.404978498878208</v>
       </c>
       <c r="G7">
-        <v>1.390972419996553</v>
+        <v>1.383621814052024</v>
       </c>
       <c r="H7">
-        <v>1.349955890124775</v>
+        <v>1.349480192554219</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -556,22 +556,22 @@
         <v>1.419552146857844</v>
       </c>
       <c r="C8">
-        <v>1.286428854980599</v>
+        <v>1.311923632743135</v>
       </c>
       <c r="D8">
         <v>1.149297017754301</v>
       </c>
       <c r="E8">
-        <v>1.34067164994444</v>
+        <v>1.34053287489543</v>
       </c>
       <c r="F8">
         <v>1.409312192220709</v>
       </c>
       <c r="G8">
-        <v>1.307684694103237</v>
+        <v>1.325207859392255</v>
       </c>
       <c r="H8">
-        <v>1.340676964773854</v>
+        <v>1.340521949481359</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -582,22 +582,22 @@
         <v>1.426263507133462</v>
       </c>
       <c r="C9">
-        <v>1.366023141857575</v>
+        <v>1.350241973754367</v>
       </c>
       <c r="D9">
         <v>0.8337038804962448</v>
       </c>
       <c r="E9">
-        <v>1.344961376309288</v>
+        <v>1.344502126473592</v>
       </c>
       <c r="F9">
         <v>1.419164020447879</v>
       </c>
       <c r="G9">
-        <v>1.359680543457173</v>
+        <v>1.35583694564875</v>
       </c>
       <c r="H9">
-        <v>1.34534416732288</v>
+        <v>1.344885643389748</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -608,22 +608,22 @@
         <v>1.225441711943756</v>
       </c>
       <c r="C10">
-        <v>1.409810408930863</v>
+        <v>1.376002053963837</v>
       </c>
       <c r="D10">
         <v>2.973400820959877</v>
       </c>
       <c r="E10">
-        <v>1.33803734195631</v>
+        <v>1.337604876518737</v>
       </c>
       <c r="F10">
         <v>1.272247449763021</v>
       </c>
       <c r="G10">
-        <v>1.403891052508207</v>
+        <v>1.381485396026643</v>
       </c>
       <c r="H10">
-        <v>1.339021721330762</v>
+        <v>1.338586669553266</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -634,22 +634,22 @@
         <v>1.183188477810486</v>
       </c>
       <c r="C11">
-        <v>1.414360880002127</v>
+        <v>1.382149816534359</v>
       </c>
       <c r="D11">
         <v>2.583480844780975</v>
       </c>
       <c r="E11">
-        <v>1.339872308311111</v>
+        <v>1.339440020619098</v>
       </c>
       <c r="F11">
         <v>1.23236576267096</v>
       </c>
       <c r="G11">
-        <v>1.400737064552015</v>
+        <v>1.37830874562257</v>
       </c>
       <c r="H11">
-        <v>1.340293742975245</v>
+        <v>1.339860055703738</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -660,22 +660,22 @@
         <v>0.9765449706184234</v>
       </c>
       <c r="C12">
-        <v>1.405296775565356</v>
+        <v>1.368489245568724</v>
       </c>
       <c r="D12">
         <v>1.194841888868513</v>
       </c>
       <c r="E12">
-        <v>1.324747553747766</v>
+        <v>1.324309626005364</v>
       </c>
       <c r="F12">
         <v>0.9993215601058448</v>
       </c>
       <c r="G12">
-        <v>1.373175483619288</v>
+        <v>1.351087570385829</v>
       </c>
       <c r="H12">
-        <v>1.324371252076056</v>
+        <v>1.32393441237671</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -686,22 +686,22 @@
         <v>1.211683814326919</v>
       </c>
       <c r="C13">
-        <v>1.408286739559427</v>
+        <v>1.373166809191563</v>
       </c>
       <c r="D13">
         <v>2.47231477791947</v>
       </c>
       <c r="E13">
-        <v>1.335620606451475</v>
+        <v>1.335180309218462</v>
       </c>
       <c r="F13">
         <v>1.24896039519903</v>
       </c>
       <c r="G13">
-        <v>1.392783088423188</v>
+        <v>1.370516843988449</v>
       </c>
       <c r="H13">
-        <v>1.336020726629191</v>
+        <v>1.335577775097917</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_hoog.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_hoog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Zone</t>
   </si>
@@ -28,7 +28,10 @@
     <t>OV</t>
   </si>
   <si>
-    <t>Auto-FietsOV_Fiets</t>
+    <t>Auto-Fiets</t>
+  </si>
+  <si>
+    <t>OV_Fiets</t>
   </si>
   <si>
     <t>Auto_OV</t>
@@ -391,6 +394,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
